--- a/2-Section- Basic Excel/data/07 Supply Chain.xlsx
+++ b/2-Section- Basic Excel/data/07 Supply Chain.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29902"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sumit\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a6ce4a7617f1ad9/Desktop/courses/Data Analytics/2-Section- Basic Excel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13D4ADBC-AF45-43D3-90D8-4CF0E6C3D872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{13D4ADBC-AF45-43D3-90D8-4CF0E6C3D872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F58F5D-EC16-4042-A75A-C786F9ACD469}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{DBAEF54B-1DB0-4C64-80FA-51752F4CBAFD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DBAEF54B-1DB0-4C64-80FA-51752F4CBAFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Supply Chain" sheetId="1" r:id="rId1"/>
+    <sheet name="My Tables " sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Supply Chain'!$A$1:$K$1001</definedName>
@@ -30,8 +31,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -41,8 +40,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6011" uniqueCount="1046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6033" uniqueCount="1063">
   <si>
     <t>Shipment ID</t>
   </si>
@@ -3180,6 +3201,57 @@
   </si>
   <si>
     <t>SHP-41000</t>
+  </si>
+  <si>
+    <t>S.no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty </t>
+  </si>
+  <si>
+    <t>categories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Categories  Supply  Chain  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Cost  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total  Cost  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping Carrier cost  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplier Details </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suppiler  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">qty  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping  Modes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">S.no </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shipping Modes </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Years  Cost  </t>
+  </si>
+  <si>
+    <t>S.No</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year </t>
   </si>
 </sst>
 </file>
@@ -3190,7 +3262,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3206,8 +3278,24 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3220,8 +3308,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -3229,11 +3329,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3241,6 +3356,19 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3577,22 +3705,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDF28A70-FA35-4658-B88B-70C9431CF949}">
   <sheetPr codeName="Sheet8"/>
   <dimension ref="A1:K1001"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.5546875" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" customWidth="1"/>
+    <col min="4" max="4" width="19.109375" customWidth="1"/>
+    <col min="5" max="5" width="11.77734375" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="19.109375" customWidth="1"/>
+    <col min="10" max="10" width="19.5546875" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3627,7 +3754,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -3662,7 +3789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -3697,7 +3824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -3732,7 +3859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -3767,7 +3894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -3802,7 +3929,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>32</v>
       </c>
@@ -3837,7 +3964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -3872,7 +3999,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -3907,7 +4034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>38</v>
       </c>
@@ -3942,7 +4069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -3977,7 +4104,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -4012,7 +4139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>44</v>
       </c>
@@ -4047,7 +4174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -4082,7 +4209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>49</v>
       </c>
@@ -4117,7 +4244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>50</v>
       </c>
@@ -4152,7 +4279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>51</v>
       </c>
@@ -4187,7 +4314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>53</v>
       </c>
@@ -4222,7 +4349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>55</v>
       </c>
@@ -4257,7 +4384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>56</v>
       </c>
@@ -4292,7 +4419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -4327,7 +4454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>58</v>
       </c>
@@ -4362,7 +4489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -4397,7 +4524,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>60</v>
       </c>
@@ -4432,7 +4559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -4467,7 +4594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>65</v>
       </c>
@@ -4502,7 +4629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -4537,7 +4664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -4572,7 +4699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -4607,7 +4734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -4642,7 +4769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>71</v>
       </c>
@@ -4677,7 +4804,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>73</v>
       </c>
@@ -4712,7 +4839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>74</v>
       </c>
@@ -4747,7 +4874,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>75</v>
       </c>
@@ -4782,7 +4909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>76</v>
       </c>
@@ -4817,7 +4944,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>78</v>
       </c>
@@ -4852,7 +4979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>80</v>
       </c>
@@ -4887,7 +5014,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -4922,7 +5049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>82</v>
       </c>
@@ -4957,7 +5084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>83</v>
       </c>
@@ -4992,7 +5119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>84</v>
       </c>
@@ -5027,7 +5154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>86</v>
       </c>
@@ -5062,7 +5189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>87</v>
       </c>
@@ -5097,7 +5224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>88</v>
       </c>
@@ -5132,7 +5259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>89</v>
       </c>
@@ -5167,7 +5294,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>90</v>
       </c>
@@ -5202,7 +5329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>91</v>
       </c>
@@ -5237,7 +5364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>92</v>
       </c>
@@ -5272,7 +5399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>93</v>
       </c>
@@ -5307,7 +5434,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>94</v>
       </c>
@@ -5342,7 +5469,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>95</v>
       </c>
@@ -5377,7 +5504,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -5412,7 +5539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>97</v>
       </c>
@@ -5447,7 +5574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>98</v>
       </c>
@@ -5482,7 +5609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>99</v>
       </c>
@@ -5517,7 +5644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>100</v>
       </c>
@@ -5552,7 +5679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>101</v>
       </c>
@@ -5587,7 +5714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>102</v>
       </c>
@@ -5622,7 +5749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>103</v>
       </c>
@@ -5657,7 +5784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>104</v>
       </c>
@@ -5692,7 +5819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>105</v>
       </c>
@@ -5727,7 +5854,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>106</v>
       </c>
@@ -5762,7 +5889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>107</v>
       </c>
@@ -5797,7 +5924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>108</v>
       </c>
@@ -5832,7 +5959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>109</v>
       </c>
@@ -5867,7 +5994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>110</v>
       </c>
@@ -5902,7 +6029,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>111</v>
       </c>
@@ -5937,7 +6064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>112</v>
       </c>
@@ -5972,7 +6099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>113</v>
       </c>
@@ -6007,7 +6134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>114</v>
       </c>
@@ -6042,7 +6169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>115</v>
       </c>
@@ -6077,7 +6204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>116</v>
       </c>
@@ -6112,7 +6239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>117</v>
       </c>
@@ -6147,7 +6274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>118</v>
       </c>
@@ -6182,7 +6309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>119</v>
       </c>
@@ -6217,7 +6344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>120</v>
       </c>
@@ -6252,7 +6379,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>121</v>
       </c>
@@ -6287,7 +6414,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>122</v>
       </c>
@@ -6322,7 +6449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>123</v>
       </c>
@@ -6357,7 +6484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>124</v>
       </c>
@@ -6392,7 +6519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>125</v>
       </c>
@@ -6427,7 +6554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>126</v>
       </c>
@@ -6462,7 +6589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>127</v>
       </c>
@@ -6497,7 +6624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>128</v>
       </c>
@@ -6532,7 +6659,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>129</v>
       </c>
@@ -6567,7 +6694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>130</v>
       </c>
@@ -6602,7 +6729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>131</v>
       </c>
@@ -6637,7 +6764,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>132</v>
       </c>
@@ -6672,7 +6799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>133</v>
       </c>
@@ -6707,7 +6834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>134</v>
       </c>
@@ -6742,7 +6869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>135</v>
       </c>
@@ -6777,7 +6904,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>136</v>
       </c>
@@ -6812,7 +6939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>137</v>
       </c>
@@ -6847,7 +6974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>138</v>
       </c>
@@ -6882,7 +7009,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>139</v>
       </c>
@@ -6917,7 +7044,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>140</v>
       </c>
@@ -6952,7 +7079,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>141</v>
       </c>
@@ -6987,7 +7114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>142</v>
       </c>
@@ -7022,7 +7149,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>143</v>
       </c>
@@ -7057,7 +7184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>144</v>
       </c>
@@ -7092,7 +7219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>145</v>
       </c>
@@ -7127,7 +7254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>146</v>
       </c>
@@ -7162,7 +7289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>147</v>
       </c>
@@ -7197,7 +7324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>148</v>
       </c>
@@ -7232,7 +7359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>149</v>
       </c>
@@ -7267,7 +7394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>150</v>
       </c>
@@ -7302,7 +7429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>151</v>
       </c>
@@ -7337,7 +7464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>152</v>
       </c>
@@ -7372,7 +7499,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>153</v>
       </c>
@@ -7407,7 +7534,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>154</v>
       </c>
@@ -7442,7 +7569,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>155</v>
       </c>
@@ -7477,7 +7604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>156</v>
       </c>
@@ -7512,7 +7639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>157</v>
       </c>
@@ -7547,7 +7674,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>158</v>
       </c>
@@ -7582,7 +7709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>159</v>
       </c>
@@ -7617,7 +7744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>160</v>
       </c>
@@ -7652,7 +7779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>161</v>
       </c>
@@ -7687,7 +7814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>162</v>
       </c>
@@ -7722,7 +7849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>163</v>
       </c>
@@ -7757,7 +7884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>164</v>
       </c>
@@ -7792,7 +7919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>165</v>
       </c>
@@ -7827,7 +7954,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>166</v>
       </c>
@@ -7862,7 +7989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>167</v>
       </c>
@@ -7897,7 +8024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>168</v>
       </c>
@@ -7932,7 +8059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>169</v>
       </c>
@@ -7967,7 +8094,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>170</v>
       </c>
@@ -8002,7 +8129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>171</v>
       </c>
@@ -8037,7 +8164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>172</v>
       </c>
@@ -8072,7 +8199,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>173</v>
       </c>
@@ -8107,7 +8234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>174</v>
       </c>
@@ -8142,7 +8269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>175</v>
       </c>
@@ -8177,7 +8304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>176</v>
       </c>
@@ -8212,7 +8339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>177</v>
       </c>
@@ -8247,7 +8374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>178</v>
       </c>
@@ -8282,7 +8409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>179</v>
       </c>
@@ -8317,7 +8444,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>180</v>
       </c>
@@ -8352,7 +8479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>181</v>
       </c>
@@ -8387,7 +8514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>182</v>
       </c>
@@ -8422,7 +8549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>183</v>
       </c>
@@ -8457,7 +8584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>184</v>
       </c>
@@ -8492,7 +8619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>185</v>
       </c>
@@ -8527,7 +8654,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>186</v>
       </c>
@@ -8562,7 +8689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>187</v>
       </c>
@@ -8597,7 +8724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>188</v>
       </c>
@@ -8632,7 +8759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>189</v>
       </c>
@@ -8667,7 +8794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>190</v>
       </c>
@@ -8702,7 +8829,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>191</v>
       </c>
@@ -8737,7 +8864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>192</v>
       </c>
@@ -8772,7 +8899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>193</v>
       </c>
@@ -8807,7 +8934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>194</v>
       </c>
@@ -8842,7 +8969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>195</v>
       </c>
@@ -8877,7 +9004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>196</v>
       </c>
@@ -8912,7 +9039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>197</v>
       </c>
@@ -8947,7 +9074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>198</v>
       </c>
@@ -8982,7 +9109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>199</v>
       </c>
@@ -9017,7 +9144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>200</v>
       </c>
@@ -9052,7 +9179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>201</v>
       </c>
@@ -9087,7 +9214,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>202</v>
       </c>
@@ -9122,7 +9249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>203</v>
       </c>
@@ -9157,7 +9284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>204</v>
       </c>
@@ -9192,7 +9319,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>205</v>
       </c>
@@ -9227,7 +9354,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>206</v>
       </c>
@@ -9262,7 +9389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>207</v>
       </c>
@@ -9297,7 +9424,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>208</v>
       </c>
@@ -9332,7 +9459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>209</v>
       </c>
@@ -9367,7 +9494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>210</v>
       </c>
@@ -9402,7 +9529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>211</v>
       </c>
@@ -9437,7 +9564,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>212</v>
       </c>
@@ -9472,7 +9599,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>213</v>
       </c>
@@ -9507,7 +9634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>214</v>
       </c>
@@ -9542,7 +9669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>215</v>
       </c>
@@ -9577,7 +9704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>216</v>
       </c>
@@ -9612,7 +9739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>217</v>
       </c>
@@ -9647,7 +9774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>218</v>
       </c>
@@ -9682,7 +9809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>219</v>
       </c>
@@ -9717,7 +9844,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>220</v>
       </c>
@@ -9752,7 +9879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>221</v>
       </c>
@@ -9787,7 +9914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>222</v>
       </c>
@@ -9822,7 +9949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>223</v>
       </c>
@@ -9857,7 +9984,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>224</v>
       </c>
@@ -9892,7 +10019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>225</v>
       </c>
@@ -9927,7 +10054,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>226</v>
       </c>
@@ -9962,7 +10089,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>227</v>
       </c>
@@ -9997,7 +10124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>228</v>
       </c>
@@ -10032,7 +10159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>229</v>
       </c>
@@ -10067,7 +10194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>230</v>
       </c>
@@ -10102,7 +10229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>231</v>
       </c>
@@ -10137,7 +10264,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>232</v>
       </c>
@@ -10172,7 +10299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>233</v>
       </c>
@@ -10207,7 +10334,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>234</v>
       </c>
@@ -10242,7 +10369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>235</v>
       </c>
@@ -10277,7 +10404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>236</v>
       </c>
@@ -10312,7 +10439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="193" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>237</v>
       </c>
@@ -10347,7 +10474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="194" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>238</v>
       </c>
@@ -10382,7 +10509,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="195" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>239</v>
       </c>
@@ -10417,7 +10544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="196" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>240</v>
       </c>
@@ -10452,7 +10579,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="197" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>241</v>
       </c>
@@ -10487,7 +10614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="198" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>242</v>
       </c>
@@ -10522,7 +10649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="199" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>243</v>
       </c>
@@ -10557,7 +10684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="200" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>244</v>
       </c>
@@ -10592,7 +10719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="201" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>245</v>
       </c>
@@ -10627,7 +10754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="202" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>246</v>
       </c>
@@ -10662,7 +10789,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="203" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>247</v>
       </c>
@@ -10697,7 +10824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="204" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>248</v>
       </c>
@@ -10732,7 +10859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="205" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>249</v>
       </c>
@@ -10767,7 +10894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="206" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>250</v>
       </c>
@@ -10802,7 +10929,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="207" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>251</v>
       </c>
@@ -10837,7 +10964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="208" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>252</v>
       </c>
@@ -10872,7 +10999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="209" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>253</v>
       </c>
@@ -10907,7 +11034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="210" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>254</v>
       </c>
@@ -10942,7 +11069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="211" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>255</v>
       </c>
@@ -10977,7 +11104,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="212" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>256</v>
       </c>
@@ -11012,7 +11139,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="213" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>257</v>
       </c>
@@ -11047,7 +11174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="214" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>258</v>
       </c>
@@ -11082,7 +11209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="215" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>259</v>
       </c>
@@ -11117,7 +11244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="216" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>260</v>
       </c>
@@ -11152,7 +11279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="217" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>261</v>
       </c>
@@ -11187,7 +11314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="218" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>262</v>
       </c>
@@ -11222,7 +11349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="219" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>263</v>
       </c>
@@ -11257,7 +11384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="220" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>264</v>
       </c>
@@ -11292,7 +11419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="221" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>265</v>
       </c>
@@ -11327,7 +11454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="222" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>266</v>
       </c>
@@ -11362,7 +11489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="223" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>267</v>
       </c>
@@ -11397,7 +11524,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="224" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>268</v>
       </c>
@@ -11432,7 +11559,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="225" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>269</v>
       </c>
@@ -11467,7 +11594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="226" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>270</v>
       </c>
@@ -11502,7 +11629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="227" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>271</v>
       </c>
@@ -11537,7 +11664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="228" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>272</v>
       </c>
@@ -11572,7 +11699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="229" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>273</v>
       </c>
@@ -11607,7 +11734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="230" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>274</v>
       </c>
@@ -11642,7 +11769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="231" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>275</v>
       </c>
@@ -11677,7 +11804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="232" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>276</v>
       </c>
@@ -11712,7 +11839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="233" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>277</v>
       </c>
@@ -11747,7 +11874,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="234" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>278</v>
       </c>
@@ -11782,7 +11909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="235" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>279</v>
       </c>
@@ -11817,7 +11944,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="236" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>280</v>
       </c>
@@ -11852,7 +11979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>281</v>
       </c>
@@ -11887,7 +12014,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="238" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>282</v>
       </c>
@@ -11922,7 +12049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="239" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>283</v>
       </c>
@@ -11957,7 +12084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="240" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>284</v>
       </c>
@@ -11992,7 +12119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="241" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>285</v>
       </c>
@@ -12027,7 +12154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="242" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>286</v>
       </c>
@@ -12062,7 +12189,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="243" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>287</v>
       </c>
@@ -12097,7 +12224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>288</v>
       </c>
@@ -12132,7 +12259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="245" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>289</v>
       </c>
@@ -12167,7 +12294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="246" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>290</v>
       </c>
@@ -12202,7 +12329,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="247" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>291</v>
       </c>
@@ -12237,7 +12364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="248" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>292</v>
       </c>
@@ -12272,7 +12399,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="249" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>293</v>
       </c>
@@ -12307,7 +12434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="250" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>294</v>
       </c>
@@ -12342,7 +12469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="251" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>295</v>
       </c>
@@ -12377,7 +12504,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="252" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>296</v>
       </c>
@@ -12412,7 +12539,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="253" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>297</v>
       </c>
@@ -12447,7 +12574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="254" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>298</v>
       </c>
@@ -12482,7 +12609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="255" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>299</v>
       </c>
@@ -12517,7 +12644,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="256" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>300</v>
       </c>
@@ -12552,7 +12679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="257" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>301</v>
       </c>
@@ -12587,7 +12714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="258" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>302</v>
       </c>
@@ -12622,7 +12749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="259" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>303</v>
       </c>
@@ -12657,7 +12784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="260" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>304</v>
       </c>
@@ -12692,7 +12819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="261" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>305</v>
       </c>
@@ -12727,7 +12854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="262" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>306</v>
       </c>
@@ -12762,7 +12889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="263" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>307</v>
       </c>
@@ -12797,7 +12924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="264" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>308</v>
       </c>
@@ -12832,7 +12959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="265" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>309</v>
       </c>
@@ -12867,7 +12994,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="266" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>310</v>
       </c>
@@ -12902,7 +13029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="267" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>311</v>
       </c>
@@ -12937,7 +13064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="268" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>312</v>
       </c>
@@ -12972,7 +13099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="269" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>313</v>
       </c>
@@ -13007,7 +13134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="270" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>314</v>
       </c>
@@ -13042,7 +13169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="271" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>315</v>
       </c>
@@ -13077,7 +13204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="272" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>316</v>
       </c>
@@ -13112,7 +13239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="273" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>317</v>
       </c>
@@ -13147,7 +13274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="274" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>318</v>
       </c>
@@ -13182,7 +13309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="275" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>319</v>
       </c>
@@ -13217,7 +13344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="276" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>320</v>
       </c>
@@ -13252,7 +13379,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="277" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>321</v>
       </c>
@@ -13287,7 +13414,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="278" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>322</v>
       </c>
@@ -13322,7 +13449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="279" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>323</v>
       </c>
@@ -13357,7 +13484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="280" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>324</v>
       </c>
@@ -13392,7 +13519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="281" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>325</v>
       </c>
@@ -13427,7 +13554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="282" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>326</v>
       </c>
@@ -13462,7 +13589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="283" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>327</v>
       </c>
@@ -13497,7 +13624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="284" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>328</v>
       </c>
@@ -13532,7 +13659,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="285" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>329</v>
       </c>
@@ -13567,7 +13694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="286" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>330</v>
       </c>
@@ -13602,7 +13729,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="287" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>331</v>
       </c>
@@ -13637,7 +13764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="288" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>332</v>
       </c>
@@ -13672,7 +13799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="289" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>333</v>
       </c>
@@ -13707,7 +13834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="290" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>334</v>
       </c>
@@ -13742,7 +13869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="291" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>335</v>
       </c>
@@ -13777,7 +13904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="292" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>336</v>
       </c>
@@ -13812,7 +13939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="293" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>337</v>
       </c>
@@ -13847,7 +13974,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="294" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>338</v>
       </c>
@@ -13882,7 +14009,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="295" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>339</v>
       </c>
@@ -13917,7 +14044,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="296" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>340</v>
       </c>
@@ -13952,7 +14079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="297" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>341</v>
       </c>
@@ -13987,7 +14114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="298" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>342</v>
       </c>
@@ -14022,7 +14149,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="299" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>343</v>
       </c>
@@ -14057,7 +14184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="300" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>344</v>
       </c>
@@ -14092,7 +14219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>345</v>
       </c>
@@ -14127,7 +14254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="302" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>346</v>
       </c>
@@ -14162,7 +14289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="303" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>347</v>
       </c>
@@ -14197,7 +14324,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="304" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>348</v>
       </c>
@@ -14232,7 +14359,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="305" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>349</v>
       </c>
@@ -14267,7 +14394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="306" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>350</v>
       </c>
@@ -14302,7 +14429,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="307" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>351</v>
       </c>
@@ -14337,7 +14464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="308" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>352</v>
       </c>
@@ -14372,7 +14499,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="309" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>353</v>
       </c>
@@ -14407,7 +14534,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="310" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>354</v>
       </c>
@@ -14442,7 +14569,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="311" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>355</v>
       </c>
@@ -14477,7 +14604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="312" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>356</v>
       </c>
@@ -14512,7 +14639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="313" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>357</v>
       </c>
@@ -14547,7 +14674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="314" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>358</v>
       </c>
@@ -14582,7 +14709,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="315" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>359</v>
       </c>
@@ -14617,7 +14744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="316" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>360</v>
       </c>
@@ -14652,7 +14779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="317" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>361</v>
       </c>
@@ -14687,7 +14814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="318" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>362</v>
       </c>
@@ -14722,7 +14849,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="319" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>363</v>
       </c>
@@ -14757,7 +14884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="320" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>364</v>
       </c>
@@ -14792,7 +14919,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="321" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>365</v>
       </c>
@@ -14827,7 +14954,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="322" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>366</v>
       </c>
@@ -14862,7 +14989,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>367</v>
       </c>
@@ -14897,7 +15024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="324" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>368</v>
       </c>
@@ -14932,7 +15059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>369</v>
       </c>
@@ -14967,7 +15094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="326" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>370</v>
       </c>
@@ -15002,7 +15129,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="327" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>371</v>
       </c>
@@ -15037,7 +15164,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="328" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>372</v>
       </c>
@@ -15072,7 +15199,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="329" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>373</v>
       </c>
@@ -15107,7 +15234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="330" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>374</v>
       </c>
@@ -15142,7 +15269,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="331" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>375</v>
       </c>
@@ -15177,7 +15304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="332" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>376</v>
       </c>
@@ -15212,7 +15339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="333" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>377</v>
       </c>
@@ -15247,7 +15374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="334" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>378</v>
       </c>
@@ -15282,7 +15409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="335" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>379</v>
       </c>
@@ -15317,7 +15444,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="336" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>380</v>
       </c>
@@ -15352,7 +15479,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="337" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>381</v>
       </c>
@@ -15387,7 +15514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="338" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>382</v>
       </c>
@@ -15422,7 +15549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="339" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>383</v>
       </c>
@@ -15457,7 +15584,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="340" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>384</v>
       </c>
@@ -15492,7 +15619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="341" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>385</v>
       </c>
@@ -15527,7 +15654,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="342" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>386</v>
       </c>
@@ -15562,7 +15689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="343" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>387</v>
       </c>
@@ -15597,7 +15724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="344" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>388</v>
       </c>
@@ -15632,7 +15759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="345" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>389</v>
       </c>
@@ -15667,7 +15794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="346" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>390</v>
       </c>
@@ -15702,7 +15829,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="347" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>391</v>
       </c>
@@ -15737,7 +15864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="348" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>392</v>
       </c>
@@ -15772,7 +15899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="349" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>393</v>
       </c>
@@ -15807,7 +15934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="350" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>394</v>
       </c>
@@ -15842,7 +15969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="351" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>395</v>
       </c>
@@ -15877,7 +16004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="352" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>396</v>
       </c>
@@ -15912,7 +16039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="353" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>397</v>
       </c>
@@ -15947,7 +16074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="354" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>398</v>
       </c>
@@ -15982,7 +16109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="355" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>399</v>
       </c>
@@ -16017,7 +16144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="356" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>400</v>
       </c>
@@ -16052,7 +16179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="357" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>401</v>
       </c>
@@ -16087,7 +16214,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="358" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>402</v>
       </c>
@@ -16122,7 +16249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="359" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>403</v>
       </c>
@@ -16157,7 +16284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="360" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>404</v>
       </c>
@@ -16192,7 +16319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="361" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>405</v>
       </c>
@@ -16227,7 +16354,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="362" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>406</v>
       </c>
@@ -16262,7 +16389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="363" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>407</v>
       </c>
@@ -16297,7 +16424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="364" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>408</v>
       </c>
@@ -16332,7 +16459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="365" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>409</v>
       </c>
@@ -16367,7 +16494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="366" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>410</v>
       </c>
@@ -16402,7 +16529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="367" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>411</v>
       </c>
@@ -16437,7 +16564,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="368" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>412</v>
       </c>
@@ -16472,7 +16599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="369" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>413</v>
       </c>
@@ -16507,7 +16634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="370" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>414</v>
       </c>
@@ -16542,7 +16669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="371" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>415</v>
       </c>
@@ -16577,7 +16704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="372" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>416</v>
       </c>
@@ -16612,7 +16739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="373" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>417</v>
       </c>
@@ -16647,7 +16774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="374" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>418</v>
       </c>
@@ -16682,7 +16809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="375" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>419</v>
       </c>
@@ -16717,7 +16844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="376" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>420</v>
       </c>
@@ -16752,7 +16879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="377" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>421</v>
       </c>
@@ -16787,7 +16914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="378" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>422</v>
       </c>
@@ -16822,7 +16949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="379" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>423</v>
       </c>
@@ -16857,7 +16984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="380" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>424</v>
       </c>
@@ -16892,7 +17019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="381" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>425</v>
       </c>
@@ -16927,7 +17054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="382" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>426</v>
       </c>
@@ -16962,7 +17089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="383" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>427</v>
       </c>
@@ -16997,7 +17124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="384" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>428</v>
       </c>
@@ -17032,7 +17159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="385" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>429</v>
       </c>
@@ -17067,7 +17194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="386" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>430</v>
       </c>
@@ -17102,7 +17229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="387" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>431</v>
       </c>
@@ -17137,7 +17264,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="388" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>432</v>
       </c>
@@ -17172,7 +17299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="389" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>433</v>
       </c>
@@ -17207,7 +17334,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="390" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>434</v>
       </c>
@@ -17242,7 +17369,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="391" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>435</v>
       </c>
@@ -17277,7 +17404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="392" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>436</v>
       </c>
@@ -17312,7 +17439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="393" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>437</v>
       </c>
@@ -17347,7 +17474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="394" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>438</v>
       </c>
@@ -17382,7 +17509,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="395" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>439</v>
       </c>
@@ -17417,7 +17544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="396" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>440</v>
       </c>
@@ -17452,7 +17579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="397" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>441</v>
       </c>
@@ -17487,7 +17614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="398" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>442</v>
       </c>
@@ -17522,7 +17649,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="399" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>443</v>
       </c>
@@ -17557,7 +17684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="400" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>444</v>
       </c>
@@ -17592,7 +17719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="401" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>445</v>
       </c>
@@ -17627,7 +17754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="402" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>446</v>
       </c>
@@ -17662,7 +17789,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="403" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>447</v>
       </c>
@@ -17697,7 +17824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="404" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>448</v>
       </c>
@@ -17732,7 +17859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="405" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>449</v>
       </c>
@@ -17767,7 +17894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="406" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>450</v>
       </c>
@@ -17802,7 +17929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="407" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>451</v>
       </c>
@@ -17837,7 +17964,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="408" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>452</v>
       </c>
@@ -17872,7 +17999,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="409" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>453</v>
       </c>
@@ -17907,7 +18034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="410" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>454</v>
       </c>
@@ -17942,7 +18069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="411" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>455</v>
       </c>
@@ -17977,7 +18104,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="412" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>456</v>
       </c>
@@ -18012,7 +18139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="413" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>457</v>
       </c>
@@ -18047,7 +18174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="414" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>458</v>
       </c>
@@ -18082,7 +18209,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="415" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>459</v>
       </c>
@@ -18117,7 +18244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="416" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>460</v>
       </c>
@@ -18152,7 +18279,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="417" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>461</v>
       </c>
@@ -18187,7 +18314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="418" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>462</v>
       </c>
@@ -18222,7 +18349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="419" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>463</v>
       </c>
@@ -18257,7 +18384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="420" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>464</v>
       </c>
@@ -18292,7 +18419,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="421" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>465</v>
       </c>
@@ -18327,7 +18454,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="422" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>466</v>
       </c>
@@ -18362,7 +18489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="423" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>467</v>
       </c>
@@ -18397,7 +18524,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="424" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>468</v>
       </c>
@@ -18432,7 +18559,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="425" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>469</v>
       </c>
@@ -18467,7 +18594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="426" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>470</v>
       </c>
@@ -18502,7 +18629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="427" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>471</v>
       </c>
@@ -18537,7 +18664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="428" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>472</v>
       </c>
@@ -18572,7 +18699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="429" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>473</v>
       </c>
@@ -18607,7 +18734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="430" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>474</v>
       </c>
@@ -18642,7 +18769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="431" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>475</v>
       </c>
@@ -18677,7 +18804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="432" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>476</v>
       </c>
@@ -18712,7 +18839,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="433" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>477</v>
       </c>
@@ -18747,7 +18874,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="434" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>478</v>
       </c>
@@ -18782,7 +18909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="435" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>479</v>
       </c>
@@ -18817,7 +18944,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="436" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>480</v>
       </c>
@@ -18852,7 +18979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="437" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>481</v>
       </c>
@@ -18887,7 +19014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="438" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>482</v>
       </c>
@@ -18922,7 +19049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="439" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>483</v>
       </c>
@@ -18957,7 +19084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="440" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>484</v>
       </c>
@@ -18992,7 +19119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="441" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>485</v>
       </c>
@@ -19027,7 +19154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="442" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>486</v>
       </c>
@@ -19062,7 +19189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="443" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>487</v>
       </c>
@@ -19097,7 +19224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="444" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>488</v>
       </c>
@@ -19132,7 +19259,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="445" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>489</v>
       </c>
@@ -19167,7 +19294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="446" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>490</v>
       </c>
@@ -19202,7 +19329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="447" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>491</v>
       </c>
@@ -19237,7 +19364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="448" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>492</v>
       </c>
@@ -19272,7 +19399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="449" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>493</v>
       </c>
@@ -19307,7 +19434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="450" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>494</v>
       </c>
@@ -19342,7 +19469,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="451" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>495</v>
       </c>
@@ -19377,7 +19504,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="452" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>496</v>
       </c>
@@ -19412,7 +19539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="453" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>497</v>
       </c>
@@ -19447,7 +19574,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="454" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>498</v>
       </c>
@@ -19482,7 +19609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="455" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>499</v>
       </c>
@@ -19517,7 +19644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="456" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>500</v>
       </c>
@@ -19552,7 +19679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="457" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>501</v>
       </c>
@@ -19587,7 +19714,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="458" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>502</v>
       </c>
@@ -19622,7 +19749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="459" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>503</v>
       </c>
@@ -19657,7 +19784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="460" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>504</v>
       </c>
@@ -19692,7 +19819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="461" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>505</v>
       </c>
@@ -19727,7 +19854,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="462" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>506</v>
       </c>
@@ -19762,7 +19889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="463" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>507</v>
       </c>
@@ -19797,7 +19924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="464" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>508</v>
       </c>
@@ -19832,7 +19959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="465" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>509</v>
       </c>
@@ -19867,7 +19994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="466" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>510</v>
       </c>
@@ -19902,7 +20029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="467" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>511</v>
       </c>
@@ -19937,7 +20064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="468" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>512</v>
       </c>
@@ -19972,7 +20099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="469" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>513</v>
       </c>
@@ -20007,7 +20134,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="470" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>514</v>
       </c>
@@ -20042,7 +20169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="471" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>515</v>
       </c>
@@ -20077,7 +20204,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="472" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>516</v>
       </c>
@@ -20112,7 +20239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="473" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>517</v>
       </c>
@@ -20147,7 +20274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="474" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>518</v>
       </c>
@@ -20182,7 +20309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="475" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>519</v>
       </c>
@@ -20217,7 +20344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="476" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>520</v>
       </c>
@@ -20252,7 +20379,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="477" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>521</v>
       </c>
@@ -20287,7 +20414,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="478" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>522</v>
       </c>
@@ -20322,7 +20449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="479" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>523</v>
       </c>
@@ -20357,7 +20484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="480" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>524</v>
       </c>
@@ -20392,7 +20519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="481" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>525</v>
       </c>
@@ -20427,7 +20554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="482" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>526</v>
       </c>
@@ -20462,7 +20589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="483" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>527</v>
       </c>
@@ -20497,7 +20624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="484" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>528</v>
       </c>
@@ -20532,7 +20659,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="485" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>529</v>
       </c>
@@ -20567,7 +20694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="486" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>530</v>
       </c>
@@ -20602,7 +20729,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="487" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>531</v>
       </c>
@@ -20637,7 +20764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="488" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>532</v>
       </c>
@@ -20672,7 +20799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="489" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>533</v>
       </c>
@@ -20707,7 +20834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="490" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>534</v>
       </c>
@@ -20742,7 +20869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="491" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>535</v>
       </c>
@@ -20777,7 +20904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="492" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>536</v>
       </c>
@@ -20812,7 +20939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="493" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>537</v>
       </c>
@@ -20847,7 +20974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="494" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>538</v>
       </c>
@@ -20882,7 +21009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="495" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>539</v>
       </c>
@@ -20917,7 +21044,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="496" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>540</v>
       </c>
@@ -20952,7 +21079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="497" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>541</v>
       </c>
@@ -20987,7 +21114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="498" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>542</v>
       </c>
@@ -21022,7 +21149,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="499" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>543</v>
       </c>
@@ -21057,7 +21184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="500" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>544</v>
       </c>
@@ -21092,7 +21219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="501" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>545</v>
       </c>
@@ -21127,7 +21254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="502" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>546</v>
       </c>
@@ -21162,7 +21289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="503" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>547</v>
       </c>
@@ -21197,7 +21324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="504" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>548</v>
       </c>
@@ -21232,7 +21359,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="505" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>549</v>
       </c>
@@ -21267,7 +21394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="506" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>550</v>
       </c>
@@ -21302,7 +21429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="507" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>551</v>
       </c>
@@ -21337,7 +21464,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="508" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>552</v>
       </c>
@@ -21372,7 +21499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="509" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>553</v>
       </c>
@@ -21407,7 +21534,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="510" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>554</v>
       </c>
@@ -21442,7 +21569,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="511" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>555</v>
       </c>
@@ -21477,7 +21604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="512" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>556</v>
       </c>
@@ -21512,7 +21639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="513" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>557</v>
       </c>
@@ -21547,7 +21674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="514" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>558</v>
       </c>
@@ -21582,7 +21709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="515" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>559</v>
       </c>
@@ -21617,7 +21744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="516" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>560</v>
       </c>
@@ -21652,7 +21779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="517" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>561</v>
       </c>
@@ -21687,7 +21814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="518" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>562</v>
       </c>
@@ -21722,7 +21849,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="519" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>563</v>
       </c>
@@ -21757,7 +21884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="520" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>564</v>
       </c>
@@ -21792,7 +21919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="521" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>565</v>
       </c>
@@ -21827,7 +21954,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="522" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>566</v>
       </c>
@@ -21862,7 +21989,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="523" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>567</v>
       </c>
@@ -21897,7 +22024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="524" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>568</v>
       </c>
@@ -21932,7 +22059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="525" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>569</v>
       </c>
@@ -21967,7 +22094,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="526" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>570</v>
       </c>
@@ -22002,7 +22129,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="527" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>571</v>
       </c>
@@ -22037,7 +22164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="528" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>572</v>
       </c>
@@ -22072,7 +22199,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="529" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>573</v>
       </c>
@@ -22107,7 +22234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="530" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>574</v>
       </c>
@@ -22142,7 +22269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="531" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>575</v>
       </c>
@@ -22177,7 +22304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="532" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>576</v>
       </c>
@@ -22212,7 +22339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="533" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>577</v>
       </c>
@@ -22247,7 +22374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="534" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>578</v>
       </c>
@@ -22282,7 +22409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="535" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>579</v>
       </c>
@@ -22317,7 +22444,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="536" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>580</v>
       </c>
@@ -22352,7 +22479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="537" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>581</v>
       </c>
@@ -22387,7 +22514,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="538" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>582</v>
       </c>
@@ -22422,7 +22549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="539" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>583</v>
       </c>
@@ -22457,7 +22584,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="540" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>584</v>
       </c>
@@ -22492,7 +22619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="541" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>585</v>
       </c>
@@ -22527,7 +22654,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="542" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>586</v>
       </c>
@@ -22562,7 +22689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="543" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>587</v>
       </c>
@@ -22597,7 +22724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="544" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>588</v>
       </c>
@@ -22632,7 +22759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="545" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>589</v>
       </c>
@@ -22667,7 +22794,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="546" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>590</v>
       </c>
@@ -22702,7 +22829,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="547" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>591</v>
       </c>
@@ -22737,7 +22864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="548" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>592</v>
       </c>
@@ -22772,7 +22899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="549" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>593</v>
       </c>
@@ -22807,7 +22934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="550" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>594</v>
       </c>
@@ -22842,7 +22969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="551" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>595</v>
       </c>
@@ -22877,7 +23004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="552" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>596</v>
       </c>
@@ -22912,7 +23039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="553" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>597</v>
       </c>
@@ -22947,7 +23074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="554" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>598</v>
       </c>
@@ -22982,7 +23109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="555" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>599</v>
       </c>
@@ -23017,7 +23144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="556" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>600</v>
       </c>
@@ -23052,7 +23179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="557" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>601</v>
       </c>
@@ -23087,7 +23214,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="558" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>602</v>
       </c>
@@ -23122,7 +23249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="559" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>603</v>
       </c>
@@ -23157,7 +23284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="560" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>604</v>
       </c>
@@ -23192,7 +23319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="561" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>605</v>
       </c>
@@ -23227,7 +23354,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="562" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>606</v>
       </c>
@@ -23262,7 +23389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="563" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>607</v>
       </c>
@@ -23297,7 +23424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="564" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>608</v>
       </c>
@@ -23332,7 +23459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="565" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>609</v>
       </c>
@@ -23367,7 +23494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="566" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>610</v>
       </c>
@@ -23402,7 +23529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="567" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>611</v>
       </c>
@@ -23437,7 +23564,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="568" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>612</v>
       </c>
@@ -23472,7 +23599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="569" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>613</v>
       </c>
@@ -23507,7 +23634,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="570" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>614</v>
       </c>
@@ -23542,7 +23669,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="571" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>615</v>
       </c>
@@ -23577,7 +23704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="572" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>616</v>
       </c>
@@ -23612,7 +23739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="573" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>617</v>
       </c>
@@ -23647,7 +23774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="574" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>618</v>
       </c>
@@ -23682,7 +23809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="575" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>619</v>
       </c>
@@ -23717,7 +23844,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="576" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>620</v>
       </c>
@@ -23752,7 +23879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="577" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>621</v>
       </c>
@@ -23787,7 +23914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="578" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>622</v>
       </c>
@@ -23822,7 +23949,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="579" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>623</v>
       </c>
@@ -23857,7 +23984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="580" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>624</v>
       </c>
@@ -23892,7 +24019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="581" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>625</v>
       </c>
@@ -23927,7 +24054,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="582" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>626</v>
       </c>
@@ -23962,7 +24089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="583" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>627</v>
       </c>
@@ -23997,7 +24124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="584" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>628</v>
       </c>
@@ -24032,7 +24159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="585" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>629</v>
       </c>
@@ -24067,7 +24194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="586" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>630</v>
       </c>
@@ -24102,7 +24229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="587" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>631</v>
       </c>
@@ -24137,7 +24264,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="588" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>632</v>
       </c>
@@ -24172,7 +24299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="589" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>633</v>
       </c>
@@ -24207,7 +24334,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="590" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>634</v>
       </c>
@@ -24242,7 +24369,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="591" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>635</v>
       </c>
@@ -24277,7 +24404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="592" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>636</v>
       </c>
@@ -24312,7 +24439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="593" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>637</v>
       </c>
@@ -24347,7 +24474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="594" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>638</v>
       </c>
@@ -24382,7 +24509,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="595" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>639</v>
       </c>
@@ -24417,7 +24544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="596" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>640</v>
       </c>
@@ -24452,7 +24579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="597" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>641</v>
       </c>
@@ -24487,7 +24614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="598" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>642</v>
       </c>
@@ -24522,7 +24649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="599" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>643</v>
       </c>
@@ -24557,7 +24684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="600" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>644</v>
       </c>
@@ -24592,7 +24719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="601" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>645</v>
       </c>
@@ -24627,7 +24754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="602" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>646</v>
       </c>
@@ -24662,7 +24789,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="603" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>647</v>
       </c>
@@ -24697,7 +24824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="604" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>648</v>
       </c>
@@ -24732,7 +24859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="605" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>649</v>
       </c>
@@ -24767,7 +24894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="606" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>650</v>
       </c>
@@ -24802,7 +24929,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="607" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>651</v>
       </c>
@@ -24837,7 +24964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="608" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>652</v>
       </c>
@@ -24872,7 +24999,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="609" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>653</v>
       </c>
@@ -24907,7 +25034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="610" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>654</v>
       </c>
@@ -24942,7 +25069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="611" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>655</v>
       </c>
@@ -24977,7 +25104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="612" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>656</v>
       </c>
@@ -25012,7 +25139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="613" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>657</v>
       </c>
@@ -25047,7 +25174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="614" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>658</v>
       </c>
@@ -25082,7 +25209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="615" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>659</v>
       </c>
@@ -25117,7 +25244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="616" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>660</v>
       </c>
@@ -25152,7 +25279,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="617" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>661</v>
       </c>
@@ -25187,7 +25314,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="618" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>662</v>
       </c>
@@ -25222,7 +25349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="619" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>663</v>
       </c>
@@ -25257,7 +25384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="620" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>664</v>
       </c>
@@ -25292,7 +25419,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="621" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>665</v>
       </c>
@@ -25327,7 +25454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="622" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>666</v>
       </c>
@@ -25362,7 +25489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="623" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>667</v>
       </c>
@@ -25397,7 +25524,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="624" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>668</v>
       </c>
@@ -25432,7 +25559,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="625" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>669</v>
       </c>
@@ -25467,7 +25594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="626" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>670</v>
       </c>
@@ -25502,7 +25629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="627" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>671</v>
       </c>
@@ -25537,7 +25664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="628" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>672</v>
       </c>
@@ -25572,7 +25699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="629" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>673</v>
       </c>
@@ -25607,7 +25734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="630" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>674</v>
       </c>
@@ -25642,7 +25769,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="631" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>675</v>
       </c>
@@ -25677,7 +25804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="632" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>676</v>
       </c>
@@ -25712,7 +25839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="633" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>677</v>
       </c>
@@ -25747,7 +25874,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="634" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>678</v>
       </c>
@@ -25782,7 +25909,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="635" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>679</v>
       </c>
@@ -25817,7 +25944,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="636" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>680</v>
       </c>
@@ -25852,7 +25979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="637" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>681</v>
       </c>
@@ -25887,7 +26014,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="638" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>682</v>
       </c>
@@ -25922,7 +26049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="639" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>683</v>
       </c>
@@ -25957,7 +26084,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="640" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>684</v>
       </c>
@@ -25992,7 +26119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="641" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>685</v>
       </c>
@@ -26027,7 +26154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="642" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>686</v>
       </c>
@@ -26062,7 +26189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="643" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>687</v>
       </c>
@@ -26097,7 +26224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="644" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>688</v>
       </c>
@@ -26132,7 +26259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="645" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>689</v>
       </c>
@@ -26167,7 +26294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="646" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>690</v>
       </c>
@@ -26202,7 +26329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="647" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>691</v>
       </c>
@@ -26237,7 +26364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="648" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>692</v>
       </c>
@@ -26272,7 +26399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="649" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>693</v>
       </c>
@@ -26307,7 +26434,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="650" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>694</v>
       </c>
@@ -26342,7 +26469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="651" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>695</v>
       </c>
@@ -26377,7 +26504,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="652" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>696</v>
       </c>
@@ -26412,7 +26539,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="653" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>697</v>
       </c>
@@ -26447,7 +26574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="654" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>698</v>
       </c>
@@ -26482,7 +26609,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="655" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>699</v>
       </c>
@@ -26517,7 +26644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="656" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>700</v>
       </c>
@@ -26552,7 +26679,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="657" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>701</v>
       </c>
@@ -26587,7 +26714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="658" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>702</v>
       </c>
@@ -26622,7 +26749,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="659" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>703</v>
       </c>
@@ -26657,7 +26784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="660" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>704</v>
       </c>
@@ -26692,7 +26819,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="661" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>705</v>
       </c>
@@ -26727,7 +26854,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="662" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>706</v>
       </c>
@@ -26762,7 +26889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="663" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>707</v>
       </c>
@@ -26797,7 +26924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="664" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>708</v>
       </c>
@@ -26832,7 +26959,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="665" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>709</v>
       </c>
@@ -26867,7 +26994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="666" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>710</v>
       </c>
@@ -26902,7 +27029,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="667" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>711</v>
       </c>
@@ -26937,7 +27064,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="668" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>712</v>
       </c>
@@ -26972,7 +27099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="669" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>713</v>
       </c>
@@ -27007,7 +27134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="670" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>714</v>
       </c>
@@ -27042,7 +27169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="671" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>715</v>
       </c>
@@ -27077,7 +27204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="672" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>716</v>
       </c>
@@ -27112,7 +27239,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="673" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>717</v>
       </c>
@@ -27147,7 +27274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="674" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>718</v>
       </c>
@@ -27182,7 +27309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="675" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>719</v>
       </c>
@@ -27217,7 +27344,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="676" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>720</v>
       </c>
@@ -27252,7 +27379,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="677" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>721</v>
       </c>
@@ -27287,7 +27414,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="678" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>722</v>
       </c>
@@ -27322,7 +27449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="679" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>723</v>
       </c>
@@ -27357,7 +27484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="680" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>724</v>
       </c>
@@ -27392,7 +27519,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="681" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>725</v>
       </c>
@@ -27427,7 +27554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="682" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>726</v>
       </c>
@@ -27462,7 +27589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="683" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>727</v>
       </c>
@@ -27497,7 +27624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="684" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>728</v>
       </c>
@@ -27532,7 +27659,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="685" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>729</v>
       </c>
@@ -27567,7 +27694,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="686" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>730</v>
       </c>
@@ -27602,7 +27729,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="687" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>731</v>
       </c>
@@ -27637,7 +27764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="688" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>732</v>
       </c>
@@ -27672,7 +27799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="689" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>733</v>
       </c>
@@ -27707,7 +27834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="690" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>734</v>
       </c>
@@ -27742,7 +27869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="691" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>735</v>
       </c>
@@ -27777,7 +27904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="692" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>736</v>
       </c>
@@ -27812,7 +27939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="693" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>737</v>
       </c>
@@ -27847,7 +27974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="694" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>738</v>
       </c>
@@ -27882,7 +28009,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="695" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>739</v>
       </c>
@@ -27917,7 +28044,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="696" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>740</v>
       </c>
@@ -27952,7 +28079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="697" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>741</v>
       </c>
@@ -27987,7 +28114,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="698" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>742</v>
       </c>
@@ -28022,7 +28149,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="699" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>743</v>
       </c>
@@ -28057,7 +28184,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="700" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>744</v>
       </c>
@@ -28092,7 +28219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="701" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>745</v>
       </c>
@@ -28127,7 +28254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="702" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>746</v>
       </c>
@@ -28162,7 +28289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="703" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>747</v>
       </c>
@@ -28197,7 +28324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="704" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>748</v>
       </c>
@@ -28232,7 +28359,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="705" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>749</v>
       </c>
@@ -28267,7 +28394,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="706" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>750</v>
       </c>
@@ -28302,7 +28429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="707" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>751</v>
       </c>
@@ -28337,7 +28464,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="708" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>752</v>
       </c>
@@ -28372,7 +28499,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="709" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>753</v>
       </c>
@@ -28407,7 +28534,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="710" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>754</v>
       </c>
@@ -28442,7 +28569,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="711" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>755</v>
       </c>
@@ -28477,7 +28604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="712" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>756</v>
       </c>
@@ -28512,7 +28639,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="713" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>757</v>
       </c>
@@ -28547,7 +28674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="714" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>758</v>
       </c>
@@ -28582,7 +28709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="715" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>759</v>
       </c>
@@ -28617,7 +28744,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="716" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>760</v>
       </c>
@@ -28652,7 +28779,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="717" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>761</v>
       </c>
@@ -28687,7 +28814,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="718" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>762</v>
       </c>
@@ -28722,7 +28849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="719" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>763</v>
       </c>
@@ -28757,7 +28884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="720" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>764</v>
       </c>
@@ -28792,7 +28919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="721" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>765</v>
       </c>
@@ -28827,7 +28954,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="722" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>766</v>
       </c>
@@ -28862,7 +28989,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="723" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>767</v>
       </c>
@@ -28897,7 +29024,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="724" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>768</v>
       </c>
@@ -28932,7 +29059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="725" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>769</v>
       </c>
@@ -28967,7 +29094,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="726" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>770</v>
       </c>
@@ -29002,7 +29129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="727" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>771</v>
       </c>
@@ -29037,7 +29164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="728" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>772</v>
       </c>
@@ -29072,7 +29199,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="729" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>773</v>
       </c>
@@ -29107,7 +29234,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="730" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>774</v>
       </c>
@@ -29142,7 +29269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="731" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>775</v>
       </c>
@@ -29177,7 +29304,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="732" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>776</v>
       </c>
@@ -29212,7 +29339,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="733" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>777</v>
       </c>
@@ -29247,7 +29374,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="734" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>778</v>
       </c>
@@ -29282,7 +29409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="735" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>779</v>
       </c>
@@ -29317,7 +29444,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="736" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>780</v>
       </c>
@@ -29352,7 +29479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="737" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>781</v>
       </c>
@@ -29387,7 +29514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="738" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>782</v>
       </c>
@@ -29422,7 +29549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="739" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>783</v>
       </c>
@@ -29457,7 +29584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="740" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>784</v>
       </c>
@@ -29492,7 +29619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="741" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>785</v>
       </c>
@@ -29527,7 +29654,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="742" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>786</v>
       </c>
@@ -29562,7 +29689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="743" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>787</v>
       </c>
@@ -29597,7 +29724,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="744" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>788</v>
       </c>
@@ -29632,7 +29759,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="745" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>789</v>
       </c>
@@ -29667,7 +29794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="746" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>790</v>
       </c>
@@ -29702,7 +29829,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="747" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>791</v>
       </c>
@@ -29737,7 +29864,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="748" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>792</v>
       </c>
@@ -29772,7 +29899,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="749" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>793</v>
       </c>
@@ -29807,7 +29934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="750" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>794</v>
       </c>
@@ -29842,7 +29969,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="751" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>795</v>
       </c>
@@ -29877,7 +30004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="752" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>796</v>
       </c>
@@ -29912,7 +30039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="753" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>797</v>
       </c>
@@ -29947,7 +30074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="754" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>798</v>
       </c>
@@ -29982,7 +30109,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="755" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>799</v>
       </c>
@@ -30017,7 +30144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="756" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>800</v>
       </c>
@@ -30052,7 +30179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="757" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>801</v>
       </c>
@@ -30087,7 +30214,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="758" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>802</v>
       </c>
@@ -30122,7 +30249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="759" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>803</v>
       </c>
@@ -30157,7 +30284,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="760" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>804</v>
       </c>
@@ -30192,7 +30319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="761" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>805</v>
       </c>
@@ -30227,7 +30354,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="762" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>806</v>
       </c>
@@ -30262,7 +30389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="763" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>807</v>
       </c>
@@ -30297,7 +30424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="764" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>808</v>
       </c>
@@ -30332,7 +30459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="765" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>809</v>
       </c>
@@ -30367,7 +30494,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="766" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>810</v>
       </c>
@@ -30402,7 +30529,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="767" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>811</v>
       </c>
@@ -30437,7 +30564,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="768" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>812</v>
       </c>
@@ -30472,7 +30599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="769" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>813</v>
       </c>
@@ -30507,7 +30634,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="770" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>814</v>
       </c>
@@ -30542,7 +30669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="771" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>815</v>
       </c>
@@ -30577,7 +30704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="772" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>816</v>
       </c>
@@ -30612,7 +30739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="773" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>817</v>
       </c>
@@ -30647,7 +30774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="774" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>818</v>
       </c>
@@ -30682,7 +30809,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="775" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>819</v>
       </c>
@@ -30717,7 +30844,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="776" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>820</v>
       </c>
@@ -30752,7 +30879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="777" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>821</v>
       </c>
@@ -30787,7 +30914,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="778" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>822</v>
       </c>
@@ -30822,7 +30949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="779" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>823</v>
       </c>
@@ -30857,7 +30984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="780" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>824</v>
       </c>
@@ -30892,7 +31019,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="781" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>825</v>
       </c>
@@ -30927,7 +31054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="782" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>826</v>
       </c>
@@ -30962,7 +31089,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="783" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>827</v>
       </c>
@@ -30997,7 +31124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="784" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>828</v>
       </c>
@@ -31032,7 +31159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="785" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>829</v>
       </c>
@@ -31067,7 +31194,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="786" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>830</v>
       </c>
@@ -31102,7 +31229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="787" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>831</v>
       </c>
@@ -31137,7 +31264,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="788" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>832</v>
       </c>
@@ -31172,7 +31299,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="789" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>833</v>
       </c>
@@ -31207,7 +31334,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="790" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>834</v>
       </c>
@@ -31242,7 +31369,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="791" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>835</v>
       </c>
@@ -31277,7 +31404,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="792" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>836</v>
       </c>
@@ -31312,7 +31439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="793" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>837</v>
       </c>
@@ -31347,7 +31474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="794" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>838</v>
       </c>
@@ -31382,7 +31509,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="795" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>839</v>
       </c>
@@ -31417,7 +31544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="796" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>840</v>
       </c>
@@ -31452,7 +31579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="797" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>841</v>
       </c>
@@ -31487,7 +31614,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="798" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>842</v>
       </c>
@@ -31522,7 +31649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="799" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>843</v>
       </c>
@@ -31557,7 +31684,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="800" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>844</v>
       </c>
@@ -31592,7 +31719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="801" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>845</v>
       </c>
@@ -31627,7 +31754,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="802" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>846</v>
       </c>
@@ -31662,7 +31789,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="803" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>847</v>
       </c>
@@ -31697,7 +31824,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="804" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>848</v>
       </c>
@@ -31732,7 +31859,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="805" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>849</v>
       </c>
@@ -31767,7 +31894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="806" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>850</v>
       </c>
@@ -31802,7 +31929,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="807" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>851</v>
       </c>
@@ -31837,7 +31964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="808" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>852</v>
       </c>
@@ -31872,7 +31999,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="809" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>853</v>
       </c>
@@ -31907,7 +32034,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="810" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>854</v>
       </c>
@@ -31942,7 +32069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="811" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>855</v>
       </c>
@@ -31977,7 +32104,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="812" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>856</v>
       </c>
@@ -32012,7 +32139,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="813" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>857</v>
       </c>
@@ -32047,7 +32174,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="814" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>858</v>
       </c>
@@ -32082,7 +32209,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="815" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>859</v>
       </c>
@@ -32117,7 +32244,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="816" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>860</v>
       </c>
@@ -32152,7 +32279,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="817" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>861</v>
       </c>
@@ -32187,7 +32314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="818" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>862</v>
       </c>
@@ -32222,7 +32349,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="819" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>863</v>
       </c>
@@ -32257,7 +32384,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="820" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>864</v>
       </c>
@@ -32292,7 +32419,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="821" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>865</v>
       </c>
@@ -32327,7 +32454,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="822" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>866</v>
       </c>
@@ -32362,7 +32489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="823" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>867</v>
       </c>
@@ -32397,7 +32524,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="824" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>868</v>
       </c>
@@ -32432,7 +32559,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="825" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>869</v>
       </c>
@@ -32467,7 +32594,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="826" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>870</v>
       </c>
@@ -32502,7 +32629,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="827" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>871</v>
       </c>
@@ -32537,7 +32664,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="828" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>872</v>
       </c>
@@ -32572,7 +32699,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="829" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>873</v>
       </c>
@@ -32607,7 +32734,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="830" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>874</v>
       </c>
@@ -32642,7 +32769,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="831" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>875</v>
       </c>
@@ -32677,7 +32804,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="832" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>876</v>
       </c>
@@ -32712,7 +32839,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="833" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>877</v>
       </c>
@@ -32747,7 +32874,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="834" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>878</v>
       </c>
@@ -32782,7 +32909,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="835" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>879</v>
       </c>
@@ -32817,7 +32944,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="836" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>880</v>
       </c>
@@ -32852,7 +32979,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="837" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>881</v>
       </c>
@@ -32887,7 +33014,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="838" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>882</v>
       </c>
@@ -32922,7 +33049,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="839" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>883</v>
       </c>
@@ -32957,7 +33084,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="840" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>884</v>
       </c>
@@ -32992,7 +33119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="841" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>885</v>
       </c>
@@ -33027,7 +33154,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="842" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>886</v>
       </c>
@@ -33062,7 +33189,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="843" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>887</v>
       </c>
@@ -33097,7 +33224,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="844" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>888</v>
       </c>
@@ -33132,7 +33259,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="845" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>889</v>
       </c>
@@ -33167,7 +33294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="846" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>890</v>
       </c>
@@ -33202,7 +33329,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="847" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>891</v>
       </c>
@@ -33237,7 +33364,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="848" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>892</v>
       </c>
@@ -33272,7 +33399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="849" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>893</v>
       </c>
@@ -33307,7 +33434,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="850" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>894</v>
       </c>
@@ -33342,7 +33469,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="851" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
         <v>895</v>
       </c>
@@ -33377,7 +33504,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="852" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>896</v>
       </c>
@@ -33412,7 +33539,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="853" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
         <v>897</v>
       </c>
@@ -33447,7 +33574,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="854" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>898</v>
       </c>
@@ -33482,7 +33609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="855" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>899</v>
       </c>
@@ -33517,7 +33644,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="856" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>900</v>
       </c>
@@ -33552,7 +33679,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="857" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>901</v>
       </c>
@@ -33587,7 +33714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="858" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
         <v>902</v>
       </c>
@@ -33622,7 +33749,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="859" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>903</v>
       </c>
@@ -33657,7 +33784,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="860" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>904</v>
       </c>
@@ -33692,7 +33819,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="861" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>905</v>
       </c>
@@ -33727,7 +33854,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="862" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>906</v>
       </c>
@@ -33762,7 +33889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="863" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
         <v>907</v>
       </c>
@@ -33797,7 +33924,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="864" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
         <v>908</v>
       </c>
@@ -33832,7 +33959,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="865" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
         <v>909</v>
       </c>
@@ -33867,7 +33994,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="866" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
         <v>910</v>
       </c>
@@ -33902,7 +34029,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="867" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
         <v>911</v>
       </c>
@@ -33937,7 +34064,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="868" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
         <v>912</v>
       </c>
@@ -33972,7 +34099,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="869" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
         <v>913</v>
       </c>
@@ -34007,7 +34134,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="870" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
         <v>914</v>
       </c>
@@ -34042,7 +34169,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="871" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
         <v>915</v>
       </c>
@@ -34077,7 +34204,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="872" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
         <v>916</v>
       </c>
@@ -34112,7 +34239,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="873" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
         <v>917</v>
       </c>
@@ -34147,7 +34274,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="874" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
         <v>918</v>
       </c>
@@ -34182,7 +34309,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="875" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
         <v>919</v>
       </c>
@@ -34217,7 +34344,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="876" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
         <v>920</v>
       </c>
@@ -34252,7 +34379,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="877" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
         <v>921</v>
       </c>
@@ -34287,7 +34414,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="878" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
         <v>922</v>
       </c>
@@ -34322,7 +34449,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="879" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
         <v>923</v>
       </c>
@@ -34357,7 +34484,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="880" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
         <v>924</v>
       </c>
@@ -34392,7 +34519,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="881" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
         <v>925</v>
       </c>
@@ -34427,7 +34554,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="882" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
         <v>926</v>
       </c>
@@ -34462,7 +34589,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="883" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
         <v>927</v>
       </c>
@@ -34497,7 +34624,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="884" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
         <v>928</v>
       </c>
@@ -34532,7 +34659,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="885" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
         <v>929</v>
       </c>
@@ -34567,7 +34694,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="886" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
         <v>930</v>
       </c>
@@ -34602,7 +34729,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="887" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
         <v>931</v>
       </c>
@@ -34637,7 +34764,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="888" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
         <v>932</v>
       </c>
@@ -34672,7 +34799,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="889" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
         <v>933</v>
       </c>
@@ -34707,7 +34834,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="890" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
         <v>934</v>
       </c>
@@ -34742,7 +34869,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="891" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
         <v>935</v>
       </c>
@@ -34777,7 +34904,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="892" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
         <v>936</v>
       </c>
@@ -34812,7 +34939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="893" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
         <v>937</v>
       </c>
@@ -34847,7 +34974,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="894" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
         <v>938</v>
       </c>
@@ -34882,7 +35009,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="895" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
         <v>939</v>
       </c>
@@ -34917,7 +35044,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="896" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
         <v>940</v>
       </c>
@@ -34952,7 +35079,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="897" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>941</v>
       </c>
@@ -34987,7 +35114,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="898" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>942</v>
       </c>
@@ -35022,7 +35149,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="899" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>943</v>
       </c>
@@ -35057,7 +35184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="900" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>944</v>
       </c>
@@ -35092,7 +35219,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="901" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>945</v>
       </c>
@@ -35127,7 +35254,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="902" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>946</v>
       </c>
@@ -35162,7 +35289,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="903" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>947</v>
       </c>
@@ -35197,7 +35324,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="904" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>948</v>
       </c>
@@ -35232,7 +35359,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="905" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
         <v>949</v>
       </c>
@@ -35267,7 +35394,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="906" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
         <v>950</v>
       </c>
@@ -35302,7 +35429,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="907" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
         <v>951</v>
       </c>
@@ -35337,7 +35464,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="908" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
         <v>952</v>
       </c>
@@ -35372,7 +35499,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="909" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
         <v>953</v>
       </c>
@@ -35407,7 +35534,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="910" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
         <v>954</v>
       </c>
@@ -35442,7 +35569,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="911" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
         <v>955</v>
       </c>
@@ -35477,7 +35604,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="912" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
         <v>956</v>
       </c>
@@ -35512,7 +35639,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="913" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A913" t="s">
         <v>957</v>
       </c>
@@ -35547,7 +35674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="914" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A914" t="s">
         <v>958</v>
       </c>
@@ -35582,7 +35709,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="915" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A915" t="s">
         <v>959</v>
       </c>
@@ -35617,7 +35744,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="916" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A916" t="s">
         <v>960</v>
       </c>
@@ -35652,7 +35779,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="917" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A917" t="s">
         <v>961</v>
       </c>
@@ -35687,7 +35814,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="918" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A918" t="s">
         <v>962</v>
       </c>
@@ -35722,7 +35849,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="919" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A919" t="s">
         <v>963</v>
       </c>
@@ -35757,7 +35884,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="920" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A920" t="s">
         <v>964</v>
       </c>
@@ -35792,7 +35919,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="921" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A921" t="s">
         <v>965</v>
       </c>
@@ -35827,7 +35954,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="922" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A922" t="s">
         <v>966</v>
       </c>
@@ -35862,7 +35989,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="923" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A923" t="s">
         <v>967</v>
       </c>
@@ -35897,7 +36024,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="924" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A924" t="s">
         <v>968</v>
       </c>
@@ -35932,7 +36059,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="925" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A925" t="s">
         <v>969</v>
       </c>
@@ -35967,7 +36094,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="926" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A926" t="s">
         <v>970</v>
       </c>
@@ -36002,7 +36129,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="927" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A927" t="s">
         <v>971</v>
       </c>
@@ -36037,7 +36164,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="928" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A928" t="s">
         <v>972</v>
       </c>
@@ -36072,7 +36199,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="929" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A929" t="s">
         <v>973</v>
       </c>
@@ -36107,7 +36234,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="930" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A930" t="s">
         <v>974</v>
       </c>
@@ -36142,7 +36269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="931" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A931" t="s">
         <v>975</v>
       </c>
@@ -36177,7 +36304,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="932" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A932" t="s">
         <v>976</v>
       </c>
@@ -36212,7 +36339,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="933" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A933" t="s">
         <v>977</v>
       </c>
@@ -36247,7 +36374,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="934" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A934" t="s">
         <v>978</v>
       </c>
@@ -36282,7 +36409,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="935" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A935" t="s">
         <v>979</v>
       </c>
@@ -36317,7 +36444,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="936" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A936" t="s">
         <v>980</v>
       </c>
@@ -36352,7 +36479,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="937" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A937" t="s">
         <v>981</v>
       </c>
@@ -36387,7 +36514,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="938" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A938" t="s">
         <v>982</v>
       </c>
@@ -36422,7 +36549,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="939" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A939" t="s">
         <v>983</v>
       </c>
@@ -36457,7 +36584,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="940" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A940" t="s">
         <v>984</v>
       </c>
@@ -36492,7 +36619,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="941" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A941" t="s">
         <v>985</v>
       </c>
@@ -36527,7 +36654,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="942" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A942" t="s">
         <v>986</v>
       </c>
@@ -36562,7 +36689,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="943" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A943" t="s">
         <v>987</v>
       </c>
@@ -36597,7 +36724,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="944" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A944" t="s">
         <v>988</v>
       </c>
@@ -36632,7 +36759,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="945" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A945" t="s">
         <v>989</v>
       </c>
@@ -36667,7 +36794,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="946" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A946" t="s">
         <v>990</v>
       </c>
@@ -36702,7 +36829,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="947" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A947" t="s">
         <v>991</v>
       </c>
@@ -36737,7 +36864,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="948" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A948" t="s">
         <v>992</v>
       </c>
@@ -36772,7 +36899,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="949" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A949" t="s">
         <v>993</v>
       </c>
@@ -36807,7 +36934,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="950" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A950" t="s">
         <v>994</v>
       </c>
@@ -36842,7 +36969,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="951" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A951" t="s">
         <v>995</v>
       </c>
@@ -36877,7 +37004,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="952" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A952" t="s">
         <v>996</v>
       </c>
@@ -36912,7 +37039,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="953" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A953" t="s">
         <v>997</v>
       </c>
@@ -36947,7 +37074,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="954" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A954" t="s">
         <v>998</v>
       </c>
@@ -36982,7 +37109,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="955" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A955" t="s">
         <v>999</v>
       </c>
@@ -37017,7 +37144,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="956" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A956" t="s">
         <v>1000</v>
       </c>
@@ -37052,7 +37179,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="957" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A957" t="s">
         <v>1001</v>
       </c>
@@ -37087,7 +37214,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="958" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A958" t="s">
         <v>1002</v>
       </c>
@@ -37122,7 +37249,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="959" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A959" t="s">
         <v>1003</v>
       </c>
@@ -37157,7 +37284,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="960" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A960" t="s">
         <v>1004</v>
       </c>
@@ -37192,7 +37319,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="961" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A961" t="s">
         <v>1005</v>
       </c>
@@ -37227,7 +37354,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="962" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A962" t="s">
         <v>1006</v>
       </c>
@@ -37262,7 +37389,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="963" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A963" t="s">
         <v>1007</v>
       </c>
@@ -37297,7 +37424,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="964" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A964" t="s">
         <v>1008</v>
       </c>
@@ -37332,7 +37459,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="965" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A965" t="s">
         <v>1009</v>
       </c>
@@ -37367,7 +37494,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="966" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A966" t="s">
         <v>1010</v>
       </c>
@@ -37402,7 +37529,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="967" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A967" t="s">
         <v>1011</v>
       </c>
@@ -37437,7 +37564,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="968" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A968" t="s">
         <v>1012</v>
       </c>
@@ -37472,7 +37599,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="969" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A969" t="s">
         <v>1013</v>
       </c>
@@ -37507,7 +37634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="970" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A970" t="s">
         <v>1014</v>
       </c>
@@ -37542,7 +37669,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="971" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A971" t="s">
         <v>1015</v>
       </c>
@@ -37577,7 +37704,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="972" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A972" t="s">
         <v>1016</v>
       </c>
@@ -37612,7 +37739,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="973" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A973" t="s">
         <v>1017</v>
       </c>
@@ -37647,7 +37774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="974" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A974" t="s">
         <v>1018</v>
       </c>
@@ -37682,7 +37809,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="975" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A975" t="s">
         <v>1019</v>
       </c>
@@ -37717,7 +37844,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="976" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A976" t="s">
         <v>1020</v>
       </c>
@@ -37752,7 +37879,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="977" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A977" t="s">
         <v>1021</v>
       </c>
@@ -37787,7 +37914,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="978" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A978" t="s">
         <v>1022</v>
       </c>
@@ -37822,7 +37949,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="979" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A979" t="s">
         <v>1023</v>
       </c>
@@ -37857,7 +37984,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="980" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A980" t="s">
         <v>1024</v>
       </c>
@@ -37892,7 +38019,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="981" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A981" t="s">
         <v>1025</v>
       </c>
@@ -37927,7 +38054,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="982" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A982" t="s">
         <v>1026</v>
       </c>
@@ -37962,7 +38089,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="983" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A983" t="s">
         <v>1027</v>
       </c>
@@ -37997,7 +38124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="984" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A984" t="s">
         <v>1028</v>
       </c>
@@ -38032,7 +38159,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="985" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A985" t="s">
         <v>1029</v>
       </c>
@@ -38067,7 +38194,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="986" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A986" t="s">
         <v>1030</v>
       </c>
@@ -38102,7 +38229,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="987" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A987" t="s">
         <v>1031</v>
       </c>
@@ -38137,7 +38264,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="988" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A988" t="s">
         <v>1032</v>
       </c>
@@ -38172,7 +38299,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="989" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A989" t="s">
         <v>1033</v>
       </c>
@@ -38207,7 +38334,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="990" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A990" t="s">
         <v>1034</v>
       </c>
@@ -38242,7 +38369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="991" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A991" t="s">
         <v>1035</v>
       </c>
@@ -38277,7 +38404,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="992" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A992" t="s">
         <v>1036</v>
       </c>
@@ -38312,7 +38439,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="993" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A993" t="s">
         <v>1037</v>
       </c>
@@ -38347,7 +38474,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="994" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A994" t="s">
         <v>1038</v>
       </c>
@@ -38382,7 +38509,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="995" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A995" t="s">
         <v>1039</v>
       </c>
@@ -38417,7 +38544,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="996" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A996" t="s">
         <v>1040</v>
       </c>
@@ -38452,7 +38579,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="997" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A997" t="s">
         <v>1041</v>
       </c>
@@ -38487,7 +38614,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="998" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A998" t="s">
         <v>1042</v>
       </c>
@@ -38522,7 +38649,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="999" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A999" t="s">
         <v>1043</v>
       </c>
@@ -38557,7 +38684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1000" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1000" t="s">
         <v>1044</v>
       </c>
@@ -38592,7 +38719,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="1001" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1001" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1001" t="s">
         <v>1045</v>
       </c>
@@ -38631,4 +38758,610 @@
   <autoFilter ref="A1:K1001" xr:uid="{2F2F50EB-AE45-4266-A253-E72F9E86095E}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA983059-9A1B-4BC0-B487-1BC23E39585B}">
+  <dimension ref="A1:M30"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="7.6640625" customWidth="1"/>
+    <col min="2" max="2" width="23.33203125" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" customWidth="1"/>
+    <col min="6" max="6" width="8.33203125" customWidth="1"/>
+    <col min="7" max="7" width="14.21875" customWidth="1"/>
+    <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="11" max="11" width="15.5546875" customWidth="1"/>
+    <col min="12" max="12" width="11.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="F1" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="K1" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>1047</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>1051</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>1060</v>
+      </c>
+      <c r="L2" s="9" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>1</v>
+      </c>
+      <c r="B3" s="6" t="str" cm="1">
+        <f t="array" ref="B3:B12">_xlfn.UNIQUE('Supply Chain'!D2:D1001)</f>
+        <v>Chemicals</v>
+      </c>
+      <c r="C3" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B3, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>305294</v>
+      </c>
+      <c r="D3" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B3, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>632298.25000000012</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1</v>
+      </c>
+      <c r="G3" s="6" t="str" cm="1">
+        <f t="array" ref="G3:G6">_xlfn.UNIQUE('Supply Chain'!I2:I1001)</f>
+        <v>UPS</v>
+      </c>
+      <c r="H3" s="6">
+        <f>SUMIF('Supply Chain'!$I$2:$I$1001, G3,'Supply Chain'!$F$2:$F$1001)</f>
+        <v>2497325.3000000007</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="str">
+        <v>Packaging</v>
+      </c>
+      <c r="C4" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B4, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>203957</v>
+      </c>
+      <c r="D4" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B4, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>231061.34</v>
+      </c>
+      <c r="F4" s="6">
+        <v>2</v>
+      </c>
+      <c r="G4" s="6" t="str">
+        <v>FedEx</v>
+      </c>
+      <c r="H4" s="6">
+        <f>SUMIF('Supply Chain'!$I$2:$I$1001, G4,'Supply Chain'!$F$2:$F$1001)</f>
+        <v>2758720.2000000016</v>
+      </c>
+      <c r="K4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="str">
+        <v>Machinery</v>
+      </c>
+      <c r="C5" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B5, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>263792</v>
+      </c>
+      <c r="D5" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B5, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>2694841.9</v>
+      </c>
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6" t="str">
+        <v>Local</v>
+      </c>
+      <c r="H5" s="6">
+        <f>SUMIF('Supply Chain'!$I$2:$I$1001, G5,'Supply Chain'!$F$2:$F$1001)</f>
+        <v>1077914.1100000003</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>4</v>
+      </c>
+      <c r="B6" s="6" t="str">
+        <v>Automotive Parts</v>
+      </c>
+      <c r="C6" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B6, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>271562</v>
+      </c>
+      <c r="D6" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B6, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>1160139.2600000005</v>
+      </c>
+      <c r="F6" s="6">
+        <v>4</v>
+      </c>
+      <c r="G6" s="6" t="str">
+        <v>DHL</v>
+      </c>
+      <c r="H6" s="6">
+        <f>SUMIF('Supply Chain'!$I$2:$I$1001, G6,'Supply Chain'!$F$2:$F$1001)</f>
+        <v>1942007.2100000009</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>5</v>
+      </c>
+      <c r="B7" s="6" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="C7" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B7, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>214572</v>
+      </c>
+      <c r="D7" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B7, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>1110773.3100000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="6">
+        <v>6</v>
+      </c>
+      <c r="B8" s="6" t="str">
+        <v>Textiles</v>
+      </c>
+      <c r="C8" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B8, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>194231</v>
+      </c>
+      <c r="D8" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B8, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>376313.40999999992</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>7</v>
+      </c>
+      <c r="B9" s="6" t="str">
+        <v>Raw Materials</v>
+      </c>
+      <c r="C9" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B9, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>237479</v>
+      </c>
+      <c r="D9" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B9, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>797891.83</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>8</v>
+      </c>
+      <c r="B10" s="6" t="str">
+        <v>Medical Supplies</v>
+      </c>
+      <c r="C10" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B10, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>241808</v>
+      </c>
+      <c r="D10" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B10, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>787350.38999999966</v>
+      </c>
+      <c r="F10" s="6">
+        <v>1</v>
+      </c>
+      <c r="G10" s="6" t="str" cm="1">
+        <f t="array" ref="G10:G13">_xlfn.UNIQUE('Supply Chain'!J2:J1001)</f>
+        <v>Sea</v>
+      </c>
+      <c r="H10" s="6">
+        <f>SUMIF('Supply Chain'!$J$2:$J$1001, G10, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>1133114.96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <v>9</v>
+      </c>
+      <c r="B11" s="6" t="str">
+        <v>Office Supplies</v>
+      </c>
+      <c r="C11" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B11, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>234152</v>
+      </c>
+      <c r="D11" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B11, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>150719.56000000006</v>
+      </c>
+      <c r="F11" s="6">
+        <v>2</v>
+      </c>
+      <c r="G11" s="6" t="str">
+        <v>Road</v>
+      </c>
+      <c r="H11" s="6">
+        <f>SUMIF('Supply Chain'!$J$2:$J$1001, G11, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>3935282.0900000017</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>10</v>
+      </c>
+      <c r="B12" s="6" t="str">
+        <v>Food Ingredients</v>
+      </c>
+      <c r="C12" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B12, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>231204</v>
+      </c>
+      <c r="D12" s="6">
+        <f>SUMIF('Supply Chain'!$D$2:$D$1001, B12, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>334577.56999999989</v>
+      </c>
+      <c r="F12" s="6">
+        <v>3</v>
+      </c>
+      <c r="G12" s="6" t="str">
+        <v>Rail</v>
+      </c>
+      <c r="H12" s="6">
+        <f>SUMIF('Supply Chain'!$J$2:$J$1001, G12, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>1535039.3900000011</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="F13" s="6">
+        <v>4</v>
+      </c>
+      <c r="G13" s="6" t="str">
+        <v>Air</v>
+      </c>
+      <c r="H13" s="6">
+        <f>SUMIF('Supply Chain'!$J$2:$J$1001, G13, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>1672530.3799999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="18" x14ac:dyDescent="0.35">
+      <c r="A14" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="8" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>1</v>
+      </c>
+      <c r="B16" s="6" t="str" cm="1">
+        <f t="array" ref="B16:B30">_xlfn.UNIQUE('Supply Chain'!C2:C1001)</f>
+        <v>Frontier Chemical Supply</v>
+      </c>
+      <c r="C16" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B16, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>190240</v>
+      </c>
+      <c r="D16" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B16, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>537521.36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>2</v>
+      </c>
+      <c r="B17" s="6" t="str">
+        <v>Midwest Industrial</v>
+      </c>
+      <c r="C17" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B17, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>170890</v>
+      </c>
+      <c r="D17" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B17, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>700947.73999999987</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>3</v>
+      </c>
+      <c r="B18" s="6" t="str">
+        <v>Summit Electronics</v>
+      </c>
+      <c r="C18" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B18, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>156846</v>
+      </c>
+      <c r="D18" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B18, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>627861.14999999991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>4</v>
+      </c>
+      <c r="B19" s="6" t="str">
+        <v>Continental Distributors</v>
+      </c>
+      <c r="C19" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B19, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>124497</v>
+      </c>
+      <c r="D19" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B19, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>398299.26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <v>5</v>
+      </c>
+      <c r="B20" s="6" t="str">
+        <v>Reliable Metals Corp</v>
+      </c>
+      <c r="C20" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B20, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>221013</v>
+      </c>
+      <c r="D20" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B20, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>808324.3899999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>6</v>
+      </c>
+      <c r="B21" s="6" t="str">
+        <v>Atlas Manufacturing</v>
+      </c>
+      <c r="C21" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B21, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>132053</v>
+      </c>
+      <c r="D21" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B21, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>503792.03999999992</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>7</v>
+      </c>
+      <c r="B22" s="6" t="str">
+        <v>Global Parts Inc</v>
+      </c>
+      <c r="C22" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B22, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>200255</v>
+      </c>
+      <c r="D22" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B22, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>736519.32000000018</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <v>8</v>
+      </c>
+      <c r="B23" s="6" t="str">
+        <v>Harbor Trading Co</v>
+      </c>
+      <c r="C23" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B23, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>136693</v>
+      </c>
+      <c r="D23" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B23, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>565945.81000000006</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="6">
+        <v>9</v>
+      </c>
+      <c r="B24" s="6" t="str">
+        <v>Southern Logistics</v>
+      </c>
+      <c r="C24" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B24, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>123294</v>
+      </c>
+      <c r="D24" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B24, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>384651.06</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="6">
+        <v>10</v>
+      </c>
+      <c r="B25" s="6" t="str">
+        <v>Premier Raw Materials</v>
+      </c>
+      <c r="C25" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B25, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>132239</v>
+      </c>
+      <c r="D25" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B25, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>420769.11000000004</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <v>11</v>
+      </c>
+      <c r="B26" s="6" t="str">
+        <v>Valley Fabrication</v>
+      </c>
+      <c r="C26" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B26, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>188851</v>
+      </c>
+      <c r="D26" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B26, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>543051.28999999969</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
+        <v>12</v>
+      </c>
+      <c r="B27" s="6" t="str">
+        <v>Pacific Supply Co</v>
+      </c>
+      <c r="C27" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B27, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>188561</v>
+      </c>
+      <c r="D27" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B27, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>570727.09999999986</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
+        <v>13</v>
+      </c>
+      <c r="B28" s="6" t="str">
+        <v>Pinnacle Materials</v>
+      </c>
+      <c r="C28" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B28, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>124242</v>
+      </c>
+      <c r="D28" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B28, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>388953.09</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
+        <v>14</v>
+      </c>
+      <c r="B29" s="6" t="str">
+        <v>Nordic Supply Group</v>
+      </c>
+      <c r="C29" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B29, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>127714</v>
+      </c>
+      <c r="D29" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B29, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>386208.65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <v>15</v>
+      </c>
+      <c r="B30" s="6" t="str">
+        <v>Eastern Components</v>
+      </c>
+      <c r="C30" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B30, 'Supply Chain'!$E$2:$E$1001)</f>
+        <v>180663</v>
+      </c>
+      <c r="D30" s="6">
+        <f>SUMIF('Supply Chain'!$C$2:$C$1001, B30, 'Supply Chain'!$F$2:$F$1001)</f>
+        <v>702395.45</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="K1:M1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/2-Section- Basic Excel/data/07 Supply Chain.xlsx
+++ b/2-Section- Basic Excel/data/07 Supply Chain.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8a6ce4a7617f1ad9/Desktop/courses/Data Analytics/2-Section- Basic Excel/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{13D4ADBC-AF45-43D3-90D8-4CF0E6C3D872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35F58F5D-EC16-4042-A75A-C786F9ACD469}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{13D4ADBC-AF45-43D3-90D8-4CF0E6C3D872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D2201B7-6F83-49AE-A9E6-97413E6F89F0}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{DBAEF54B-1DB0-4C64-80FA-51752F4CBAFD}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{DBAEF54B-1DB0-4C64-80FA-51752F4CBAFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Supply Chain" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6033" uniqueCount="1063">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6049" uniqueCount="1077">
   <si>
     <t>Shipment ID</t>
   </si>
@@ -3252,6 +3252,48 @@
   </si>
   <si>
     <t xml:space="preserve">Year </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales By  Months And Year </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Months </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan </t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Mar</t>
+  </si>
+  <si>
+    <t>Apr</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>Jun</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Aug</t>
+  </si>
+  <si>
+    <t>Sep</t>
+  </si>
+  <si>
+    <t>Oct</t>
+  </si>
+  <si>
+    <t>Nov</t>
+  </si>
+  <si>
+    <t>Dec</t>
   </si>
 </sst>
 </file>
@@ -3262,7 +3304,7 @@
     <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3290,6 +3332,12 @@
       <b/>
       <sz val="14"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3356,18 +3404,18 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -38762,7 +38810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA983059-9A1B-4BC0-B487-1BC23E39585B}">
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="7.6640625" customWidth="1"/>
@@ -38772,139 +38820,157 @@
     <col min="6" max="6" width="8.33203125" customWidth="1"/>
     <col min="7" max="7" width="14.21875" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="11" max="11" width="15.5546875" customWidth="1"/>
-    <col min="12" max="12" width="11.88671875" customWidth="1"/>
+    <col min="11" max="11" width="8.33203125" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
         <v>1049</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="F1" s="7" t="s">
+      <c r="B1" s="8"/>
+      <c r="C1" s="8"/>
+      <c r="D1" s="8"/>
+      <c r="F1" s="8" t="s">
         <v>1052</v>
       </c>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="K1" s="5" t="s">
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="K1" s="8" t="s">
         <v>1059</v>
       </c>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="6" t="s">
         <v>1048</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="6" t="s">
         <v>1047</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="6" t="s">
         <v>1050</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="6" t="s">
         <v>1051</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="6" t="s">
         <v>1060</v>
       </c>
-      <c r="L2" s="9" t="s">
+      <c r="L2" s="6" t="s">
         <v>1062</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="6">
+      <c r="M2" s="6" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="str" cm="1">
+      <c r="B3" s="5" t="str" cm="1">
         <f t="array" ref="B3:B12">_xlfn.UNIQUE('Supply Chain'!D2:D1001)</f>
         <v>Chemicals</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B3, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>305294</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B3, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>632298.25000000012</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>1</v>
       </c>
-      <c r="G3" s="6" t="str" cm="1">
+      <c r="G3" s="5" t="str" cm="1">
         <f t="array" ref="G3:G6">_xlfn.UNIQUE('Supply Chain'!I2:I1001)</f>
         <v>UPS</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <f>SUMIF('Supply Chain'!$I$2:$I$1001, G3,'Supply Chain'!$F$2:$F$1001)</f>
         <v>2497325.3000000007</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="5">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="6">
+      <c r="L3" s="7">
+        <v>2024</v>
+      </c>
+      <c r="M3" s="5">
+        <f>SUMIFS('Supply Chain'!F:F,'Supply Chain'!B:B,"&gt;="&amp;DATE(2024,1,1),'Supply Chain'!B:B,"&lt;"&amp;DATE(2025,1,1))</f>
+        <v>4255616.54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="str">
+      <c r="B4" s="5" t="str">
         <v>Packaging</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B4, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>203957</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B4, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>231061.34</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="6" t="str">
+      <c r="G4" s="5" t="str">
         <v>FedEx</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <f>SUMIF('Supply Chain'!$I$2:$I$1001, G4,'Supply Chain'!$F$2:$F$1001)</f>
         <v>2758720.2000000016</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="6">
+      <c r="L4" s="7">
+        <v>2025</v>
+      </c>
+      <c r="M4" s="5">
+        <f>SUMIFS('Supply Chain'!F:F,'Supply Chain'!B:B,"&gt;="&amp;DATE(2025,1,1),'Supply Chain'!B:B,"&lt;"&amp;DATE(2026,1,1))</f>
+        <v>4020350.2800000035</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="str">
+      <c r="B5" s="5" t="str">
         <v>Machinery</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B5, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>263792</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B5, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>2694841.9</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="5">
         <v>3</v>
       </c>
-      <c r="G5" s="6" t="str">
+      <c r="G5" s="5" t="str">
         <v>Local</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <f>SUMIF('Supply Chain'!$I$2:$I$1001, G5,'Supply Chain'!$F$2:$F$1001)</f>
         <v>1077914.1100000003</v>
       </c>
@@ -38912,456 +38978,549 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="6">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="str">
+      <c r="B6" s="5" t="str">
         <v>Automotive Parts</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B6, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>271562</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B6, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>1160139.2600000005</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>4</v>
       </c>
-      <c r="G6" s="6" t="str">
+      <c r="G6" s="5" t="str">
         <v>DHL</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <f>SUMIF('Supply Chain'!$I$2:$I$1001, G6,'Supply Chain'!$F$2:$F$1001)</f>
         <v>1942007.2100000009</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="6">
+      <c r="K6" s="9" t="s">
+        <v>1063</v>
+      </c>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="str">
+      <c r="B7" s="5" t="str">
         <v>Electronics</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B7, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>214572</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B7, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>1110773.3100000003</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="A8" s="6">
+      <c r="K7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1064</v>
+      </c>
+      <c r="M7">
+        <v>2024</v>
+      </c>
+      <c r="N7">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A8" s="5">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="str">
+      <c r="B8" s="5" t="str">
         <v>Textiles</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C8" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B8, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>194231</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B8, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>376313.40999999992</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="8" t="s">
         <v>1056</v>
       </c>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="6">
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>7</v>
       </c>
-      <c r="B9" s="6" t="str">
+      <c r="B9" s="5" t="str">
         <v>Raw Materials</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B9, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>237479</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B9, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>797891.83</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="F9" s="6" t="s">
         <v>1057</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="6" t="s">
         <v>1058</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="6" t="s">
         <v>1051</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="6">
+      <c r="K9">
+        <v>2</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>8</v>
       </c>
-      <c r="B10" s="6" t="str">
+      <c r="B10" s="5" t="str">
         <v>Medical Supplies</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B10, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>241808</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B10, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>787350.38999999966</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="5">
         <v>1</v>
       </c>
-      <c r="G10" s="6" t="str" cm="1">
+      <c r="G10" s="5" t="str" cm="1">
         <f t="array" ref="G10:G13">_xlfn.UNIQUE('Supply Chain'!J2:J1001)</f>
         <v>Sea</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <f>SUMIF('Supply Chain'!$J$2:$J$1001, G10, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>1133114.96</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="6">
+      <c r="K10">
+        <v>3</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>9</v>
       </c>
-      <c r="B11" s="6" t="str">
+      <c r="B11" s="5" t="str">
         <v>Office Supplies</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B11, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>234152</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B11, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>150719.56000000006</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="5">
         <v>2</v>
       </c>
-      <c r="G11" s="6" t="str">
+      <c r="G11" s="5" t="str">
         <v>Road</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <f>SUMIF('Supply Chain'!$J$2:$J$1001, G11, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>3935282.0900000017</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="6">
+      <c r="K11">
+        <v>4</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="5">
         <v>10</v>
       </c>
-      <c r="B12" s="6" t="str">
+      <c r="B12" s="5" t="str">
         <v>Food Ingredients</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B12, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>231204</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="5">
         <f>SUMIF('Supply Chain'!$D$2:$D$1001, B12, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>334577.56999999989</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="5">
         <v>3</v>
       </c>
-      <c r="G12" s="6" t="str">
+      <c r="G12" s="5" t="str">
         <v>Rail</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <f>SUMIF('Supply Chain'!$J$2:$J$1001, G12, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>1535039.3900000011</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="F13" s="6">
+      <c r="K12">
+        <v>5</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="F13" s="5">
         <v>4</v>
       </c>
-      <c r="G13" s="6" t="str">
+      <c r="G13" s="5" t="str">
         <v>Air</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <f>SUMIF('Supply Chain'!$J$2:$J$1001, G13, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>1672530.3799999997</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" ht="18" x14ac:dyDescent="0.35">
-      <c r="A14" s="7" t="s">
+      <c r="K13">
+        <v>6</v>
+      </c>
+      <c r="L13" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.35">
+      <c r="A14" s="8" t="s">
         <v>1053</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="8" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="K14">
+        <v>7</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>1046</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="6" t="s">
         <v>1054</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="6" t="s">
         <v>1055</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="6" t="s">
         <v>1050</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="6">
+      <c r="K15">
+        <v>8</v>
+      </c>
+      <c r="L15" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="B16" s="6" t="str" cm="1">
+      <c r="B16" s="5" t="str" cm="1">
         <f t="array" ref="B16:B30">_xlfn.UNIQUE('Supply Chain'!C2:C1001)</f>
         <v>Frontier Chemical Supply</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B16, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>190240</v>
       </c>
-      <c r="D16" s="6">
+      <c r="D16" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B16, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>537521.36</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="6">
+      <c r="K16">
+        <v>9</v>
+      </c>
+      <c r="L16" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="5">
         <v>2</v>
       </c>
-      <c r="B17" s="6" t="str">
+      <c r="B17" s="5" t="str">
         <v>Midwest Industrial</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B17, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>170890</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B17, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>700947.73999999987</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="6">
+      <c r="K17">
+        <v>10</v>
+      </c>
+      <c r="L17" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A18" s="5">
         <v>3</v>
       </c>
-      <c r="B18" s="6" t="str">
+      <c r="B18" s="5" t="str">
         <v>Summit Electronics</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B18, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>156846</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B18, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>627861.14999999991</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="6">
+      <c r="K18">
+        <v>11</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="5">
         <v>4</v>
       </c>
-      <c r="B19" s="6" t="str">
+      <c r="B19" s="5" t="str">
         <v>Continental Distributors</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B19, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>124497</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B19, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>398299.26</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="6">
+      <c r="K19">
+        <v>12</v>
+      </c>
+      <c r="L19" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="5">
         <v>5</v>
       </c>
-      <c r="B20" s="6" t="str">
+      <c r="B20" s="5" t="str">
         <v>Reliable Metals Corp</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B20, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>221013</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B20, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>808324.3899999999</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A21" s="6">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="5">
         <v>6</v>
       </c>
-      <c r="B21" s="6" t="str">
+      <c r="B21" s="5" t="str">
         <v>Atlas Manufacturing</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B21, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>132053</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B21, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>503792.03999999992</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A22" s="6">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="5">
         <v>7</v>
       </c>
-      <c r="B22" s="6" t="str">
+      <c r="B22" s="5" t="str">
         <v>Global Parts Inc</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B22, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>200255</v>
       </c>
-      <c r="D22" s="6">
+      <c r="D22" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B22, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>736519.32000000018</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="6">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="5">
         <v>8</v>
       </c>
-      <c r="B23" s="6" t="str">
+      <c r="B23" s="5" t="str">
         <v>Harbor Trading Co</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B23, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>136693</v>
       </c>
-      <c r="D23" s="6">
+      <c r="D23" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B23, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>565945.81000000006</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A24" s="6">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A24" s="5">
         <v>9</v>
       </c>
-      <c r="B24" s="6" t="str">
+      <c r="B24" s="5" t="str">
         <v>Southern Logistics</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B24, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>123294</v>
       </c>
-      <c r="D24" s="6">
+      <c r="D24" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B24, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>384651.06</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" s="6">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A25" s="5">
         <v>10</v>
       </c>
-      <c r="B25" s="6" t="str">
+      <c r="B25" s="5" t="str">
         <v>Premier Raw Materials</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B25, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>132239</v>
       </c>
-      <c r="D25" s="6">
+      <c r="D25" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B25, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>420769.11000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="6">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="5">
         <v>11</v>
       </c>
-      <c r="B26" s="6" t="str">
+      <c r="B26" s="5" t="str">
         <v>Valley Fabrication</v>
       </c>
-      <c r="C26" s="6">
+      <c r="C26" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B26, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>188851</v>
       </c>
-      <c r="D26" s="6">
+      <c r="D26" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B26, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>543051.28999999969</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="6">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="5">
         <v>12</v>
       </c>
-      <c r="B27" s="6" t="str">
+      <c r="B27" s="5" t="str">
         <v>Pacific Supply Co</v>
       </c>
-      <c r="C27" s="6">
+      <c r="C27" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B27, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>188561</v>
       </c>
-      <c r="D27" s="6">
+      <c r="D27" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B27, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>570727.09999999986</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A28" s="6">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="5">
         <v>13</v>
       </c>
-      <c r="B28" s="6" t="str">
+      <c r="B28" s="5" t="str">
         <v>Pinnacle Materials</v>
       </c>
-      <c r="C28" s="6">
+      <c r="C28" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B28, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>124242</v>
       </c>
-      <c r="D28" s="6">
+      <c r="D28" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B28, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>388953.09</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="6">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="5">
         <v>14</v>
       </c>
-      <c r="B29" s="6" t="str">
+      <c r="B29" s="5" t="str">
         <v>Nordic Supply Group</v>
       </c>
-      <c r="C29" s="6">
+      <c r="C29" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B29, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>127714</v>
       </c>
-      <c r="D29" s="6">
+      <c r="D29" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B29, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>386208.65</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A30" s="6">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="5">
         <v>15</v>
       </c>
-      <c r="B30" s="6" t="str">
+      <c r="B30" s="5" t="str">
         <v>Eastern Components</v>
       </c>
-      <c r="C30" s="6">
+      <c r="C30" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B30, 'Supply Chain'!$E$2:$E$1001)</f>
         <v>180663</v>
       </c>
-      <c r="D30" s="6">
+      <c r="D30" s="5">
         <f>SUMIF('Supply Chain'!$C$2:$C$1001, B30, 'Supply Chain'!$F$2:$F$1001)</f>
         <v>702395.45</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="F1:H1"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="F8:H8"/>
     <mergeCell ref="K1:M1"/>
+    <mergeCell ref="K6:N6"/>
   </mergeCells>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>